--- a/fire-alarm-matrix/output/tour-standard-22-etages-2-cages-d-escalier-garage-souterrain.xlsx
+++ b/fire-alarm-matrix/output/tour-standard-22-etages-2-cages-d-escalier-garage-souterrain.xlsx
@@ -6,10 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="Sommaire" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Matrice" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Légende" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Configuration du projet" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Références normatives" state="visible" r:id="rId8"/>
+    <sheet sheetId="3" name="Points de contrôle" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Légende" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Configuration du projet" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Références normatives" state="visible" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Matrice'!$A:$C,'Matrice'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -1076,12 +1080,67 @@
         </r>
       </text>
     </comment>
+    <comment ref="BJ1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Registres antirefoulement (barométriques) — cage(s) d'escalier pressurisée(s) — Ouverture automatique (limitation de surpression)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+          </rPr>
+          <t xml:space="preserve">NFPA-92 conception — Registres antirefoulement (barométriques) limitant la surpression dans les cages pressurisées
+CNB2015 3.2.6.3</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BK1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Avertisseur hydraulique (gong) — zone de gicleurs — Sonnerie locale actionnée par le débit d'eau
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+          </rPr>
+          <t>CNB2015 3.2.4.10 — Avertisseur hydraulique local (gong) actionné par le débit d'eau, indépendant du signal électronique au tableau</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BL1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Système de vidéosurveillance (CCTV) — Enregistrement prioritaire / rappel de la caméra de la zone en alarme au poste de sécurité
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+          </rPr>
+          <t>RBQ à confirmer — Intégration CCTV au poste de sécurité — exigence non normative incendie ; choix de conception/exploitation du bâtiment</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="423">
   <si>
     <t>MATRICE CAUSES-EFFETS — SYSTÈME D'ALARME INCENDIE</t>
   </si>
@@ -1101,7 +1160,7 @@
     <t>Préparé par : À compléter par l'ingénieur au dossier</t>
   </si>
   <si>
-    <t>Généré le : 2026-07-03 02 h 00 min 50 s</t>
+    <t>Généré le : 2026-07-03 02 h 37 min 34 s</t>
   </si>
   <si>
     <t>CONFORMITÉ RÉGLEMENTAIRE ET NORMATIVE</t>
@@ -1125,10 +1184,10 @@
     <t>⚠️ Les numéros d'article doivent être confirmés par l'ingénieur au dossier selon l'édition consolidée en vigueur et l'analyse de code du projet réel. Ce classeur constitue une base de conception défendable, pas une opinion de code scellée.</t>
   </si>
   <si>
-    <t>20 scénarios (causes) × 58 points de contrôle (effets) — voir l'onglet « Matrice »</t>
-  </si>
-  <si>
-    <t>Onglets : Sommaire · Matrice · Légende · Configuration du projet · Références normatives</t>
+    <t>22 scénarios (causes) × 61 points de contrôle (effets) — voir l'onglet « Matrice »</t>
+  </si>
+  <si>
+    <t>Onglets : Sommaire · Matrice · Points de contrôle · Légende · Configuration du projet · Références normatives</t>
   </si>
   <si>
     <t>Scénario (cause)</t>
@@ -1314,6 +1373,15 @@
     <t>ES-02</t>
   </si>
   <si>
+    <t>DF-09</t>
+  </si>
+  <si>
+    <t>GI-06</t>
+  </si>
+  <si>
+    <t>SE-01</t>
+  </si>
+  <si>
     <t>S01 — Alarme générale — détecteur de fumée en aire commune</t>
   </si>
   <si>
@@ -1434,6 +1502,12 @@
     <t>Détecteur de niveau (réservoir) ou détecteur de température basse (local chauffé)</t>
   </si>
   <si>
+    <t>S21 — Supervision — batterie du panneau de contrôle d'incendie faible ou défaillante</t>
+  </si>
+  <si>
+    <t>Circuit de supervision de la source secondaire (batteries) du panneau de contrôle d'incendie</t>
+  </si>
+  <si>
     <t>S10 — Perte de l'alimentation électrique normale</t>
   </si>
   <si>
@@ -1455,6 +1529,12 @@
     <t>POSITION-REPLI-SECURITAIRE</t>
   </si>
   <si>
+    <t>S23 — Dérangement du système de communication bidirectionnelle pompiers (DAS)</t>
+  </si>
+  <si>
+    <t>Système d'aide aux communications des services d'urgence (antenne distribuée, amplificateurs)</t>
+  </si>
+  <si>
     <t>S18 — Défaillance générale du tableau (perte CA et réserve batterie)</t>
   </si>
   <si>
@@ -1503,6 +1583,498 @@
     <t>VERROUILLE</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Discipline</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t>Système</t>
+  </si>
+  <si>
+    <t>Point commandé</t>
+  </si>
+  <si>
+    <t>Référence(s)</t>
+  </si>
+  <si>
+    <t>alarme-incendie</t>
+  </si>
+  <si>
+    <t>Protection incendie</t>
+  </si>
+  <si>
+    <t>Normale + secours</t>
+  </si>
+  <si>
+    <t>Réseau avertisseur d'incendie</t>
+  </si>
+  <si>
+    <t>Signal sonore d'alerte (ton continu)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.20 — Ton d'alerte / ton d'évacuation distincts par zone dans les bâtiments de grande hauteur ; CNB2015 3.2.4.19</t>
+  </si>
+  <si>
+    <t>Signal sonore d'évacuation (ton temporel/voix)</t>
+  </si>
+  <si>
+    <t>Communication vocale</t>
+  </si>
+  <si>
+    <t>Message vocal préenregistré d'évacuation</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.21</t>
+  </si>
+  <si>
+    <t>Message vocal préenregistré d'alerte</t>
+  </si>
+  <si>
+    <t>communication</t>
+  </si>
+  <si>
+    <t>Diffusion vocale en direct (microphone pompier/préposé)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.21 ; CNB2015 3.2.6.8</t>
+  </si>
+  <si>
+    <t>Avertisseurs visuels</t>
+  </si>
+  <si>
+    <t>Avertisseurs stroboscopiques</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.18</t>
+  </si>
+  <si>
+    <t>Tableau annonciateur principal</t>
+  </si>
+  <si>
+    <t>Indication de la zone en alarme</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.11</t>
+  </si>
+  <si>
+    <t>Répétiteur(s) d'annonciateur</t>
+  </si>
+  <si>
+    <t>Transmission à la télésurveillance</t>
+  </si>
+  <si>
+    <t>Signal transmis à la station de surveillance</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.8</t>
+  </si>
+  <si>
+    <t>Transmission au service de sécurité incendie</t>
+  </si>
+  <si>
+    <t>Signal transmis au SSI (directement ou via télésurveillance)</t>
+  </si>
+  <si>
+    <t>Verrouillage clavier (mise sous silence/réarmement inhibés)</t>
+  </si>
+  <si>
+    <t>CAN-ULC-S524 généralités</t>
+  </si>
+  <si>
+    <t>Enregistrement horodaté de l'événement</t>
+  </si>
+  <si>
+    <t>CAN-ULC-S1001 5 — Exige l'élaboration d'une matrice causes-effets comme critère d'acceptation avant les essais intégrés</t>
+  </si>
+  <si>
+    <t>desenfumage</t>
+  </si>
+  <si>
+    <t>Mécanique</t>
+  </si>
+  <si>
+    <t>Secours</t>
+  </si>
+  <si>
+    <t>Ventilateur de pressurisation — cage d'escalier A</t>
+  </si>
+  <si>
+    <t>Démarrage</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.3</t>
+  </si>
+  <si>
+    <t>Ventilateur de pressurisation — cage d'escalier B</t>
+  </si>
+  <si>
+    <t>Ventilateur d'extraction désenfumage — étage sinistré</t>
+  </si>
+  <si>
+    <t>NFPA-92 conception — Référence de dimensionnement/conception des systèmes de contrôle de fumée — usage courant en pratique québécoise</t>
+  </si>
+  <si>
+    <t>Ventilateur d'alimentation d'air — étages adjacents</t>
+  </si>
+  <si>
+    <t>volets</t>
+  </si>
+  <si>
+    <t>Registres motorisés de désenfumage — conduit d'extraction, étage sinistré</t>
+  </si>
+  <si>
+    <t>Ouverture</t>
+  </si>
+  <si>
+    <t>Registres motorisés de désenfumage — conduits des autres étages</t>
+  </si>
+  <si>
+    <t>Fermeture</t>
+  </si>
+  <si>
+    <t>Ventilateur de désenfumage — garage souterrain</t>
+  </si>
+  <si>
+    <t>Démarrage (grande vitesse / mode désenfumage)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.4 — Application au réseau d'évacuation du garage souterrain</t>
+  </si>
+  <si>
+    <t>Poste de commande des pompiers (FSCS)</t>
+  </si>
+  <si>
+    <t>Disponibilité de la commande manuelle prioritaire</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.8</t>
+  </si>
+  <si>
+    <t>evacuation-mecanique</t>
+  </si>
+  <si>
+    <t>Normale</t>
+  </si>
+  <si>
+    <t>Ventilateurs d'évacuation générale (salles de bain/cuisines communes)</t>
+  </si>
+  <si>
+    <t>Arrêt</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.4</t>
+  </si>
+  <si>
+    <t>Ventilateur d'évacuation du garage (mode qualité de l'air)</t>
+  </si>
+  <si>
+    <t>Bascule en mode désenfumage (voir DF-07) / arrêt du mode CO normal</t>
+  </si>
+  <si>
+    <t>traitement-air</t>
+  </si>
+  <si>
+    <t>Unités de traitement d'air desservant plus d'un étage</t>
+  </si>
+  <si>
+    <t>Unité de traitement d'air dédiée à la pressurisation/désenfumage</t>
+  </si>
+  <si>
+    <t>Démarrage (fonction inverse de TA-01)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.4 ; NFPA-92 conception — Référence de dimensionnement/conception des systèmes de contrôle de fumée — usage courant en pratique québécoise</t>
+  </si>
+  <si>
+    <t>Appareils de toit (RTU) desservant un seul logement</t>
+  </si>
+  <si>
+    <t>Aucune action</t>
+  </si>
+  <si>
+    <t>Volets coupe-feu — traversées de séparations coupe-feu</t>
+  </si>
+  <si>
+    <t>CNB2015 3.1.8.3</t>
+  </si>
+  <si>
+    <t>Volets coupe-fumée — gaines verticales</t>
+  </si>
+  <si>
+    <t>Fermeture (sauf ceux utilisés pour le désenfumage)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.1.8.5</t>
+  </si>
+  <si>
+    <t>Registres combinés coupe-feu/coupe-fumée motorisés — étage sinistré</t>
+  </si>
+  <si>
+    <t>Position désenfumage (ouvert ou fermé selon séquence)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.1.8.5 ; NFPA-92 conception — Référence de dimensionnement/conception des systèmes de contrôle de fumée — usage courant en pratique québécoise</t>
+  </si>
+  <si>
+    <t>ventilation-mecanique</t>
+  </si>
+  <si>
+    <t>Registres coupe-feu muraux (traversées de murs coupe-feu)</t>
+  </si>
+  <si>
+    <t>Ventilation du local de vide-ordures / local de recyclage</t>
+  </si>
+  <si>
+    <t>ascenseurs</t>
+  </si>
+  <si>
+    <t>Électricité</t>
+  </si>
+  <si>
+    <t>Tous les ascenseurs</t>
+  </si>
+  <si>
+    <t>Rappel Phase I — palier de désignation</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.9 ; CSA-B44 2.27</t>
+  </si>
+  <si>
+    <t>Rappel Phase I — bascule vers le palier alternatif</t>
+  </si>
+  <si>
+    <t>Interdiction d'arrêt/ouverture des portes à l'étage sinistré</t>
+  </si>
+  <si>
+    <t>Ascenseur désigné pompiers</t>
+  </si>
+  <si>
+    <t>Disponibilité du fonctionnement Phase II (manuel, clé pompier)</t>
+  </si>
+  <si>
+    <t>CSA-B44 2.27.3</t>
+  </si>
+  <si>
+    <t>Pressurisation de la gaine d'ascenseur</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.7</t>
+  </si>
+  <si>
+    <t>Poste de commande principal / répétiteur</t>
+  </si>
+  <si>
+    <t>Confirmation visuelle du rappel</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.6.9</t>
+  </si>
+  <si>
+    <t>Fonctionnement sélectif sur alimentation de secours</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.7.2 ; CNB2015 3.2.7.2 — Transfert automatique des charges de sécurité — délai maximal prescrit</t>
+  </si>
+  <si>
+    <t>Rappel automatique sur perte du signal (sécurité positive)</t>
+  </si>
+  <si>
+    <t>CSA-B44 2.27.3.2 — Sécurité positive — la perte du signal de rappel doit provoquer le rappel (défaillance sécuritaire)</t>
+  </si>
+  <si>
+    <t>controle-acces</t>
+  </si>
+  <si>
+    <t>Portes de contrôle d'accès sur le parcours d'évacuation</t>
+  </si>
+  <si>
+    <t>Déverrouillage</t>
+  </si>
+  <si>
+    <t>CNB2015 3.4.6.16</t>
+  </si>
+  <si>
+    <t>Porte d'accès principale — service incendie</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.5.5</t>
+  </si>
+  <si>
+    <t>Portes de contrôle d'accès hors parcours d'évacuation</t>
+  </si>
+  <si>
+    <t>Statu quo (verrouillage maintenu, selon stratégie de sécurité du projet)</t>
+  </si>
+  <si>
+    <t>portes-verrouillage</t>
+  </si>
+  <si>
+    <t>Dispositifs de retenue magnétique (portes coupe-feu maintenues ouvertes)</t>
+  </si>
+  <si>
+    <t>Relâchement (fermeture des portes)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.1.8.12 — Dispositifs de retenue en position ouverte pour portes coupe-feu — relâchement sur alarme</t>
+  </si>
+  <si>
+    <t>Portes de cage d'escalier — réentrée</t>
+  </si>
+  <si>
+    <t>Déverrouillage pour réentrée</t>
+  </si>
+  <si>
+    <t>CNB2015 3.4.6.20</t>
+  </si>
+  <si>
+    <t>generatrice</t>
+  </si>
+  <si>
+    <t>Génératrice de secours</t>
+  </si>
+  <si>
+    <t>Démarrage automatique (sur perte d'alimentation normale)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.7.1 ; CNB2015 3.2.7.2 — Transfert automatique des charges de sécurité — délai maximal prescrit</t>
+  </si>
+  <si>
+    <t>Commutateur de transfert automatique (ATS)</t>
+  </si>
+  <si>
+    <t>Transfert aux charges de sécurité incendie</t>
+  </si>
+  <si>
+    <t>Signal de fonctionnement/dérangement</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.7.1</t>
+  </si>
+  <si>
+    <t>pompes-incendie</t>
+  </si>
+  <si>
+    <t>Pompe incendie principale</t>
+  </si>
+  <si>
+    <t>Démarrage automatique (chute de pression détectée)</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.5.9</t>
+  </si>
+  <si>
+    <t>Pompe d'appoint (jockey)</t>
+  </si>
+  <si>
+    <t>Démarrage automatique (maintien de pression)</t>
+  </si>
+  <si>
+    <t>Contrôleur de pompe incendie</t>
+  </si>
+  <si>
+    <t>Signal de marche/dérangement transmis au tableau</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.5.9 ; CNB2015 3.2.4.11</t>
+  </si>
+  <si>
+    <t>Arrêt — manuel uniquement</t>
+  </si>
+  <si>
+    <t>gicleurs</t>
+  </si>
+  <si>
+    <t>Détecteur de débit d'eau (flow switch)</t>
+  </si>
+  <si>
+    <t>Signal d'alarme au tableau</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.10 — Raccordement des dispositifs de débit d'eau au système d'alarme incendie</t>
+  </si>
+  <si>
+    <t>Vanne de contrôle de zone de gicleurs</t>
+  </si>
+  <si>
+    <t>Signal de supervision — vanne fermée</t>
+  </si>
+  <si>
+    <t>Réseau de gicleurs</t>
+  </si>
+  <si>
+    <t>Signal de supervision — pression basse</t>
+  </si>
+  <si>
+    <t>Réservoir/citerne d'eau incendie</t>
+  </si>
+  <si>
+    <t>Signal de supervision — niveau bas</t>
+  </si>
+  <si>
+    <t>Local technique chauffé abritant le réseau</t>
+  </si>
+  <si>
+    <t>Signal de supervision — température basse</t>
+  </si>
+  <si>
+    <t>Système de communication bidirectionnelle pompiers (antenne distribuée)</t>
+  </si>
+  <si>
+    <t>Disponibilité continue, statut vérifié à l'alarme</t>
+  </si>
+  <si>
+    <t>RBQ à confirmer — Valider auprès des bulletins/directives RBQ en vigueur pour la juridiction du projet</t>
+  </si>
+  <si>
+    <t>eclairage-securite</t>
+  </si>
+  <si>
+    <t>Éclairage de sécurité / issues</t>
+  </si>
+  <si>
+    <t>Allumage automatique</t>
+  </si>
+  <si>
+    <t>Affichage lumineux de sortie</t>
+  </si>
+  <si>
+    <t>Alimentation confirmée par la source de secours</t>
+  </si>
+  <si>
+    <t>Registres antirefoulement (barométriques) — cage(s) d'escalier pressurisée(s)</t>
+  </si>
+  <si>
+    <t>Ouverture automatique (limitation de surpression)</t>
+  </si>
+  <si>
+    <t>NFPA-92 conception — Registres antirefoulement (barométriques) limitant la surpression dans les cages pressurisées ; CNB2015 3.2.6.3</t>
+  </si>
+  <si>
+    <t>Avertisseur hydraulique (gong) — zone de gicleurs</t>
+  </si>
+  <si>
+    <t>Sonnerie locale actionnée par le débit d'eau</t>
+  </si>
+  <si>
+    <t>CNB2015 3.2.4.10 — Avertisseur hydraulique local (gong) actionné par le débit d'eau, indépendant du signal électronique au tableau</t>
+  </si>
+  <si>
+    <t>securite-electronique</t>
+  </si>
+  <si>
+    <t>Système de vidéosurveillance (CCTV)</t>
+  </si>
+  <si>
+    <t>Enregistrement prioritaire / rappel de la caméra de la zone en alarme au poste de sécurité</t>
+  </si>
+  <si>
+    <t>RBQ à confirmer — Intégration CCTV au poste de sécurité — exigence non normative incendie ; choix de conception/exploitation du bâtiment</t>
+  </si>
+  <si>
     <t>État</t>
   </si>
   <si>
@@ -1575,6 +2147,9 @@
     <t>Code de couleur des lignes (onglet Matrice)</t>
   </si>
   <si>
+    <t>Code de couleur des disciplines (onglet Points de contrôle)</t>
+  </si>
+  <si>
     <t>Paramètre</t>
   </si>
   <si>
@@ -1629,18 +2204,9 @@
     <t>Contrôle d'accès électromagnétique</t>
   </si>
   <si>
-    <t>Communication vocale</t>
-  </si>
-  <si>
-    <t>Génératrice de secours</t>
-  </si>
-  <si>
     <t>Pompe incendie</t>
   </si>
   <si>
-    <t>Pompe d'appoint (jockey)</t>
-  </si>
-  <si>
     <t>Gicleurs partout</t>
   </si>
   <si>
@@ -1662,6 +2228,15 @@
     <t>Non</t>
   </si>
   <si>
+    <t>Vanne d'arrêt automatique du gaz naturel</t>
+  </si>
+  <si>
+    <t>Cuisine commerciale avec hotte et extinction dédiée</t>
+  </si>
+  <si>
+    <t>Vidéosurveillance (CCTV) intégrée au poste de sécurité</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -1821,7 +2396,7 @@
     <t>conception</t>
   </si>
   <si>
-    <t>Référence de dimensionnement/conception des systèmes de contrôle de fumée — usage courant en pratique québécoise</t>
+    <t>Registres antirefoulement (barométriques) limitant la surpression dans les cages pressurisées</t>
   </si>
   <si>
     <t>RBQ</t>
@@ -1830,7 +2405,7 @@
     <t>à confirmer</t>
   </si>
   <si>
-    <t>Valider auprès des bulletins/directives RBQ en vigueur pour la juridiction du projet</t>
+    <t>Dérangement du système de communication bidirectionnelle pompiers (antenne distribuée) — exigence locale à confirmer avec le service incendie</t>
   </si>
   <si>
     <t>Toutes les références ci-dessus sont mobilisées par au moins un point de contrôle ou un scénario retenu dans cette matrice. À confirmer selon l'édition consolidée en vigueur au moment du dépôt du projet.</t>
@@ -1889,7 +2464,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1931,6 +2506,21 @@
         <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE5E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF6DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1968,7 +2558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2025,6 +2615,22 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2036,6 +2642,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2378,6 +2987,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2467,8 +3077,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -2476,17 +3085,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BI21"/>
+  <dimension ref="A1:BL23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="61" width="10" customWidth="1"/>
+    <col min="4" max="64" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>16</v>
       </c>
@@ -2670,137 +3280,146 @@
       <c r="BI1" s="11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="BK1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="BL1" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V2" s="15"/>
       <c r="W2" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X2" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y2" s="15"/>
       <c r="Z2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA2" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB2" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH2" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI2" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ2" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK2" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD2" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG2" s="14" t="s">
+      <c r="AL2" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH2" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI2" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK2" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL2" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN2" s="15"/>
       <c r="AO2" s="15"/>
       <c r="AP2" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ2" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR2" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS2" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT2" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU2" s="15"/>
       <c r="AV2" s="15"/>
@@ -2815,141 +3434,148 @@
       <c r="BE2" s="15"/>
       <c r="BF2" s="15"/>
       <c r="BG2" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH2" s="15"/>
       <c r="BI2" s="15"/>
-    </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ2" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK2" s="15"/>
+      <c r="BL2" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S3" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T3" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U3" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V3" s="15"/>
       <c r="W3" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X3" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y3" s="15"/>
       <c r="Z3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA3" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA3" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB3" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE3" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ3" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK3" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD3" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE3" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF3" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AL3" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH3" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI3" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ3" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK3" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL3" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN3" s="15"/>
       <c r="AO3" s="15"/>
       <c r="AP3" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ3" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR3" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS3" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS3" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT3" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU3" s="15"/>
       <c r="AV3" s="15"/>
@@ -2964,141 +3590,148 @@
       <c r="BE3" s="15"/>
       <c r="BF3" s="15"/>
       <c r="BG3" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH3" s="15"/>
       <c r="BI3" s="15"/>
-    </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK3" s="15"/>
+      <c r="BL3" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S4" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U4" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V4" s="15"/>
       <c r="W4" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X4" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y4" s="15"/>
       <c r="Z4" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA4" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA4" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB4" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC4" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD4" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF4" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG4" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH4" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI4" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ4" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD4" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE4" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF4" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG4" s="14" t="s">
+      <c r="AL4" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH4" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI4" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ4" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL4" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN4" s="15"/>
       <c r="AO4" s="15"/>
       <c r="AP4" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ4" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS4" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS4" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT4" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU4" s="15"/>
       <c r="AV4" s="15"/>
@@ -3113,141 +3746,148 @@
       <c r="BE4" s="15"/>
       <c r="BF4" s="15"/>
       <c r="BG4" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH4" s="15"/>
       <c r="BI4" s="15"/>
-    </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ4" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK4" s="15"/>
+      <c r="BL4" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V5" s="15"/>
       <c r="W5" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X5" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y5" s="15"/>
       <c r="Z5" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA5" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA5" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB5" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC5" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD5" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE5" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI5" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ5" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK5" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD5" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE5" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF5" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG5" s="14" t="s">
+      <c r="AL5" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH5" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI5" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ5" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK5" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL5" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN5" s="15"/>
       <c r="AO5" s="15"/>
       <c r="AP5" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ5" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR5" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS5" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS5" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT5" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU5" s="15"/>
       <c r="AV5" s="15"/>
@@ -3262,147 +3902,154 @@
       <c r="BE5" s="15"/>
       <c r="BF5" s="15"/>
       <c r="BG5" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH5" s="15"/>
       <c r="BI5" s="15"/>
-    </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ5" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK5" s="15"/>
+      <c r="BL5" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S6" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U6" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V6" s="15"/>
       <c r="W6" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X6" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y6" s="15"/>
       <c r="Z6" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA6" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA6" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB6" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE6" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG6" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH6" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI6" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ6" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK6" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD6" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE6" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF6" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG6" s="14" t="s">
+      <c r="AL6" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH6" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI6" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK6" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL6" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ6" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR6" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS6" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS6" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT6" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU6" s="15"/>
       <c r="AV6" s="15"/>
       <c r="AW6" s="15"/>
       <c r="AX6" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AY6" s="15"/>
       <c r="AZ6" s="15"/>
@@ -3413,141 +4060,150 @@
       <c r="BE6" s="15"/>
       <c r="BF6" s="15"/>
       <c r="BG6" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH6" s="15"/>
       <c r="BI6" s="15"/>
-    </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ6" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK6" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="BL6" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S7" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V7" s="15"/>
       <c r="W7" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X7" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y7" s="15"/>
       <c r="Z7" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA7" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB7" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE7" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG7" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH7" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI7" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ7" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK7" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE7" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG7" s="14" t="s">
+      <c r="AL7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH7" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI7" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL7" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN7" s="15"/>
       <c r="AO7" s="15"/>
       <c r="AP7" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ7" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR7" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS7" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS7" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT7" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU7" s="15"/>
       <c r="AV7" s="15"/>
@@ -3562,145 +4218,152 @@
       <c r="BE7" s="15"/>
       <c r="BF7" s="15"/>
       <c r="BG7" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH7" s="15"/>
       <c r="BI7" s="15"/>
-    </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ7" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK7" s="15"/>
+      <c r="BL7" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R8" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S8" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="W8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="V8" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="W8" s="14" t="s">
-        <v>83</v>
-      </c>
       <c r="X8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y8" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="Y8" s="14" t="s">
+      <c r="AB8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC8" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="Z8" s="14" t="s">
+      <c r="AD8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE8" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ8" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK8" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA8" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB8" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE8" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG8" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK8" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL8" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN8" s="15"/>
       <c r="AO8" s="15"/>
       <c r="AP8" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ8" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR8" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS8" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS8" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT8" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU8" s="15"/>
       <c r="AV8" s="15"/>
@@ -3715,141 +4378,148 @@
       <c r="BE8" s="15"/>
       <c r="BF8" s="15"/>
       <c r="BG8" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH8" s="15"/>
       <c r="BI8" s="15"/>
-    </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK8" s="15"/>
+      <c r="BL8" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R9" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V9" s="15"/>
       <c r="W9" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Y9" s="15"/>
       <c r="Z9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA9" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AA9" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AB9" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC9" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD9" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE9" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF9" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH9" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AD9" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE9" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF9" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AL9" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AH9" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI9" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK9" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL9" s="14" t="s">
-        <v>84</v>
-      </c>
       <c r="AM9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AN9" s="15"/>
       <c r="AO9" s="15"/>
       <c r="AP9" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ9" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AR9" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS9" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AS9" s="14" t="s">
-        <v>86</v>
-      </c>
       <c r="AT9" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AU9" s="15"/>
       <c r="AV9" s="15"/>
@@ -3864,20 +4534,27 @@
       <c r="BE9" s="15"/>
       <c r="BF9" s="15"/>
       <c r="BG9" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BH9" s="15"/>
       <c r="BI9" s="15"/>
-    </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BK9" s="15"/>
+      <c r="BL9" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
@@ -3886,18 +4563,18 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
@@ -3936,7 +4613,7 @@
       <c r="AX10" s="15"/>
       <c r="AY10" s="15"/>
       <c r="AZ10" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BA10" s="15"/>
       <c r="BB10" s="15"/>
@@ -3947,16 +4624,19 @@
       <c r="BG10" s="15"/>
       <c r="BH10" s="15"/>
       <c r="BI10" s="15"/>
-    </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ10" s="15"/>
+      <c r="BK10" s="15"/>
+      <c r="BL10" s="15"/>
+    </row>
+    <row r="11" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -3965,13 +4645,13 @@
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
@@ -4012,7 +4692,7 @@
       <c r="AW11" s="15"/>
       <c r="AX11" s="15"/>
       <c r="AY11" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AZ11" s="15"/>
       <c r="BA11" s="15"/>
@@ -4024,16 +4704,19 @@
       <c r="BG11" s="15"/>
       <c r="BH11" s="15"/>
       <c r="BI11" s="15"/>
-    </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ11" s="15"/>
+      <c r="BK11" s="15"/>
+      <c r="BL11" s="15"/>
+    </row>
+    <row r="12" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
@@ -4042,13 +4725,13 @@
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
       <c r="J12" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -4099,16 +4782,19 @@
       <c r="BG12" s="15"/>
       <c r="BH12" s="15"/>
       <c r="BI12" s="15"/>
-    </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>119</v>
+      <c r="BJ12" s="15"/>
+      <c r="BK12" s="15"/>
+      <c r="BL12" s="15"/>
+    </row>
+    <row r="13" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -4117,15 +4803,19 @@
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="15"/>
+        <v>115</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="L13" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
+      <c r="O13" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
@@ -4150,27 +4840,17 @@
       <c r="AK13" s="15"/>
       <c r="AL13" s="15"/>
       <c r="AM13" s="15"/>
-      <c r="AN13" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="AN13" s="15"/>
       <c r="AO13" s="15"/>
       <c r="AP13" s="15"/>
       <c r="AQ13" s="15"/>
       <c r="AR13" s="15"/>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
-      <c r="AU13" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV13" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW13" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AX13" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="AU13" s="15"/>
+      <c r="AV13" s="15"/>
+      <c r="AW13" s="15"/>
+      <c r="AX13" s="15"/>
       <c r="AY13" s="15"/>
       <c r="AZ13" s="15"/>
       <c r="BA13" s="15"/>
@@ -4180,22 +4860,21 @@
       <c r="BE13" s="15"/>
       <c r="BF13" s="15"/>
       <c r="BG13" s="15"/>
-      <c r="BH13" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="BI13" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="21" t="s">
+      <c r="BH13" s="15"/>
+      <c r="BI13" s="15"/>
+      <c r="BJ13" s="15"/>
+      <c r="BK13" s="15"/>
+      <c r="BL13" s="15"/>
+    </row>
+    <row r="14" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>122</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -4204,22 +4883,16 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>112</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="K14" s="15"/>
       <c r="L14" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
-      <c r="O14" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="P14" s="14" t="s">
-        <v>123</v>
-      </c>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
       <c r="R14" s="15"/>
       <c r="S14" s="15"/>
@@ -4234,9 +4907,7 @@
       <c r="AB14" s="15"/>
       <c r="AC14" s="15"/>
       <c r="AD14" s="15"/>
-      <c r="AE14" s="14" t="s">
-        <v>123</v>
-      </c>
+      <c r="AE14" s="15"/>
       <c r="AF14" s="15"/>
       <c r="AG14" s="15"/>
       <c r="AH14" s="15"/>
@@ -4245,19 +4916,27 @@
       <c r="AK14" s="15"/>
       <c r="AL14" s="15"/>
       <c r="AM14" s="15"/>
-      <c r="AN14" s="15"/>
-      <c r="AO14" s="14" t="s">
-        <v>90</v>
-      </c>
+      <c r="AN14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO14" s="15"/>
       <c r="AP14" s="15"/>
       <c r="AQ14" s="15"/>
       <c r="AR14" s="15"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
-      <c r="AU14" s="15"/>
-      <c r="AV14" s="15"/>
-      <c r="AW14" s="15"/>
-      <c r="AX14" s="15"/>
+      <c r="AU14" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV14" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW14" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX14" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="AY14" s="15"/>
       <c r="AZ14" s="15"/>
       <c r="BA14" s="15"/>
@@ -4267,18 +4946,25 @@
       <c r="BE14" s="15"/>
       <c r="BF14" s="15"/>
       <c r="BG14" s="15"/>
-      <c r="BH14" s="15"/>
-      <c r="BI14" s="15"/>
-    </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BH14" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI14" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="BJ14" s="15"/>
+      <c r="BK14" s="15"/>
+      <c r="BL14" s="15"/>
+    </row>
+    <row r="15" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -4286,16 +4972,22 @@
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
+      <c r="J15" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="L15" s="14" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
+      <c r="O15" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="P15" s="14" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
@@ -4312,7 +5004,7 @@
       <c r="AC15" s="15"/>
       <c r="AD15" s="15"/>
       <c r="AE15" s="14" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AF15" s="15"/>
       <c r="AG15" s="15"/>
@@ -4324,14 +5016,12 @@
       <c r="AM15" s="15"/>
       <c r="AN15" s="15"/>
       <c r="AO15" s="14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AP15" s="15"/>
       <c r="AQ15" s="15"/>
       <c r="AR15" s="15"/>
-      <c r="AS15" s="14" t="s">
-        <v>86</v>
-      </c>
+      <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
       <c r="AU15" s="15"/>
       <c r="AV15" s="15"/>
@@ -4348,47 +5038,44 @@
       <c r="BG15" s="15"/>
       <c r="BH15" s="15"/>
       <c r="BI15" s="15"/>
-    </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="BJ15" s="15"/>
+      <c r="BK15" s="15"/>
+      <c r="BL15" s="15"/>
+    </row>
+    <row r="16" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>127</v>
+      <c r="C16" s="21" t="s">
+        <v>130</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
-      <c r="H16" s="14" t="s">
-        <v>83</v>
-      </c>
+      <c r="H16" s="15"/>
       <c r="I16" s="15"/>
       <c r="J16" s="14" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+      <c r="L16" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-      <c r="P16" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
-      <c r="R16" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="R16" s="15"/>
       <c r="S16" s="15"/>
       <c r="T16" s="15"/>
       <c r="U16" s="15"/>
       <c r="V16" s="15"/>
-      <c r="W16" s="14" t="s">
-        <v>128</v>
-      </c>
+      <c r="W16" s="15"/>
       <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
@@ -4396,9 +5083,7 @@
       <c r="AB16" s="15"/>
       <c r="AC16" s="15"/>
       <c r="AD16" s="15"/>
-      <c r="AE16" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="AE16" s="15"/>
       <c r="AF16" s="15"/>
       <c r="AG16" s="15"/>
       <c r="AH16" s="15"/>
@@ -4426,19 +5111,24 @@
       <c r="BD16" s="15"/>
       <c r="BE16" s="15"/>
       <c r="BF16" s="15"/>
-      <c r="BG16" s="15"/>
+      <c r="BG16" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="BH16" s="15"/>
       <c r="BI16" s="15"/>
-    </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>130</v>
+      <c r="BJ16" s="15"/>
+      <c r="BK16" s="15"/>
+      <c r="BL16" s="15"/>
+    </row>
+    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -4448,11 +5138,15 @@
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
+      <c r="L17" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
+      <c r="P17" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
@@ -4467,25 +5161,27 @@
       <c r="AB17" s="15"/>
       <c r="AC17" s="15"/>
       <c r="AD17" s="15"/>
-      <c r="AE17" s="15"/>
+      <c r="AE17" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="AF17" s="15"/>
       <c r="AG17" s="15"/>
       <c r="AH17" s="15"/>
       <c r="AI17" s="15"/>
       <c r="AJ17" s="15"/>
-      <c r="AK17" s="14" t="s">
-        <v>128</v>
-      </c>
+      <c r="AK17" s="15"/>
       <c r="AL17" s="15"/>
-      <c r="AM17" s="14" t="s">
-        <v>82</v>
-      </c>
+      <c r="AM17" s="15"/>
       <c r="AN17" s="15"/>
-      <c r="AO17" s="15"/>
+      <c r="AO17" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="AP17" s="15"/>
       <c r="AQ17" s="15"/>
       <c r="AR17" s="15"/>
-      <c r="AS17" s="15"/>
+      <c r="AS17" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="AT17" s="15"/>
       <c r="AU17" s="15"/>
       <c r="AV17" s="15"/>
@@ -4502,37 +5198,50 @@
       <c r="BG17" s="15"/>
       <c r="BH17" s="15"/>
       <c r="BI17" s="15"/>
-    </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ17" s="15"/>
+      <c r="BK17" s="15"/>
+      <c r="BL17" s="15"/>
+    </row>
+    <row r="18" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="H18" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
+      <c r="J18" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
+      <c r="P18" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
+      <c r="R18" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="S18" s="15"/>
       <c r="T18" s="15"/>
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
+      <c r="W18" s="14" t="s">
+        <v>135</v>
+      </c>
       <c r="X18" s="15"/>
       <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
@@ -4540,17 +5249,15 @@
       <c r="AB18" s="15"/>
       <c r="AC18" s="15"/>
       <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
+      <c r="AE18" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="AF18" s="15"/>
       <c r="AG18" s="15"/>
-      <c r="AH18" s="14" t="s">
-        <v>90</v>
-      </c>
+      <c r="AH18" s="15"/>
       <c r="AI18" s="15"/>
       <c r="AJ18" s="15"/>
-      <c r="AK18" s="14" t="s">
-        <v>92</v>
-      </c>
+      <c r="AK18" s="15"/>
       <c r="AL18" s="15"/>
       <c r="AM18" s="15"/>
       <c r="AN18" s="15"/>
@@ -4575,16 +5282,19 @@
       <c r="BG18" s="15"/>
       <c r="BH18" s="15"/>
       <c r="BI18" s="15"/>
-    </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>134</v>
+      <c r="BJ18" s="15"/>
+      <c r="BK18" s="15"/>
+      <c r="BL18" s="15"/>
+    </row>
+    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
@@ -4592,21 +5302,13 @@
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
-      <c r="J19" s="14" t="s">
-        <v>82</v>
-      </c>
+      <c r="J19" s="15"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="14" t="s">
-        <v>92</v>
-      </c>
+      <c r="L19" s="15"/>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
-      <c r="O19" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="P19" s="14" t="s">
-        <v>88</v>
-      </c>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
@@ -4624,24 +5326,22 @@
       <c r="AE19" s="15"/>
       <c r="AF19" s="15"/>
       <c r="AG19" s="15"/>
-      <c r="AH19" s="14" t="s">
-        <v>88</v>
-      </c>
+      <c r="AH19" s="15"/>
       <c r="AI19" s="15"/>
       <c r="AJ19" s="15"/>
-      <c r="AK19" s="15"/>
+      <c r="AK19" s="14" t="s">
+        <v>135</v>
+      </c>
       <c r="AL19" s="15"/>
-      <c r="AM19" s="15"/>
+      <c r="AM19" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="AN19" s="15"/>
       <c r="AO19" s="15"/>
-      <c r="AP19" s="14" t="s">
-        <v>88</v>
-      </c>
+      <c r="AP19" s="15"/>
       <c r="AQ19" s="15"/>
       <c r="AR19" s="15"/>
-      <c r="AS19" s="14" t="s">
-        <v>88</v>
-      </c>
+      <c r="AS19" s="15"/>
       <c r="AT19" s="15"/>
       <c r="AU19" s="15"/>
       <c r="AV19" s="15"/>
@@ -4658,40 +5358,33 @@
       <c r="BG19" s="15"/>
       <c r="BH19" s="15"/>
       <c r="BI19" s="15"/>
-    </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>88</v>
-      </c>
+      <c r="BJ19" s="15"/>
+      <c r="BK19" s="15"/>
+      <c r="BL19" s="15"/>
+    </row>
+    <row r="20" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
-      <c r="J20" s="14" t="s">
-        <v>82</v>
-      </c>
+      <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
-      <c r="O20" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="P20" s="14" t="s">
-        <v>88</v>
-      </c>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
       <c r="R20" s="15"/>
       <c r="S20" s="15"/>
@@ -4710,11 +5403,13 @@
       <c r="AF20" s="15"/>
       <c r="AG20" s="15"/>
       <c r="AH20" s="14" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AI20" s="15"/>
       <c r="AJ20" s="15"/>
-      <c r="AK20" s="15"/>
+      <c r="AK20" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="AL20" s="15"/>
       <c r="AM20" s="15"/>
       <c r="AN20" s="15"/>
@@ -4739,44 +5434,43 @@
       <c r="BG20" s="15"/>
       <c r="BH20" s="15"/>
       <c r="BI20" s="15"/>
-    </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>92</v>
-      </c>
+      <c r="BJ20" s="15"/>
+      <c r="BK20" s="15"/>
+      <c r="BL20" s="15"/>
+    </row>
+    <row r="21" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="L21" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="15"/>
-      <c r="R21" s="14" t="s">
-        <v>87</v>
-      </c>
+      <c r="R21" s="15"/>
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
@@ -4784,20 +5478,16 @@
       <c r="W21" s="15"/>
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
-      <c r="Z21" s="14" t="s">
-        <v>84</v>
-      </c>
+      <c r="Z21" s="15"/>
       <c r="AA21" s="15"/>
       <c r="AB21" s="15"/>
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
-      <c r="AE21" s="14" t="s">
-        <v>86</v>
-      </c>
+      <c r="AE21" s="15"/>
       <c r="AF21" s="15"/>
       <c r="AG21" s="15"/>
       <c r="AH21" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI21" s="15"/>
       <c r="AJ21" s="15"/>
@@ -4807,12 +5497,12 @@
       <c r="AN21" s="15"/>
       <c r="AO21" s="15"/>
       <c r="AP21" s="14" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="AQ21" s="15"/>
       <c r="AR21" s="15"/>
       <c r="AS21" s="14" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AT21" s="15"/>
       <c r="AU21" s="15"/>
@@ -4830,18 +5520,1650 @@
       <c r="BG21" s="15"/>
       <c r="BH21" s="15"/>
       <c r="BI21" s="15"/>
+      <c r="BJ21" s="15"/>
+      <c r="BK21" s="15"/>
+      <c r="BL21" s="15"/>
+    </row>
+    <row r="22" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="15"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15"/>
+      <c r="AB22" s="15"/>
+      <c r="AC22" s="15"/>
+      <c r="AD22" s="15"/>
+      <c r="AE22" s="15"/>
+      <c r="AF22" s="15"/>
+      <c r="AG22" s="15"/>
+      <c r="AH22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI22" s="15"/>
+      <c r="AJ22" s="15"/>
+      <c r="AK22" s="15"/>
+      <c r="AL22" s="15"/>
+      <c r="AM22" s="15"/>
+      <c r="AN22" s="15"/>
+      <c r="AO22" s="15"/>
+      <c r="AP22" s="15"/>
+      <c r="AQ22" s="15"/>
+      <c r="AR22" s="15"/>
+      <c r="AS22" s="15"/>
+      <c r="AT22" s="15"/>
+      <c r="AU22" s="15"/>
+      <c r="AV22" s="15"/>
+      <c r="AW22" s="15"/>
+      <c r="AX22" s="15"/>
+      <c r="AY22" s="15"/>
+      <c r="AZ22" s="15"/>
+      <c r="BA22" s="15"/>
+      <c r="BB22" s="15"/>
+      <c r="BC22" s="15"/>
+      <c r="BD22" s="15"/>
+      <c r="BE22" s="15"/>
+      <c r="BF22" s="15"/>
+      <c r="BG22" s="15"/>
+      <c r="BH22" s="15"/>
+      <c r="BI22" s="15"/>
+      <c r="BJ22" s="15"/>
+      <c r="BK22" s="15"/>
+      <c r="BL22" s="15"/>
+    </row>
+    <row r="23" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="15"/>
+      <c r="AC23" s="15"/>
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF23" s="15"/>
+      <c r="AG23" s="15"/>
+      <c r="AH23" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI23" s="15"/>
+      <c r="AJ23" s="15"/>
+      <c r="AK23" s="15"/>
+      <c r="AL23" s="15"/>
+      <c r="AM23" s="15"/>
+      <c r="AN23" s="15"/>
+      <c r="AO23" s="15"/>
+      <c r="AP23" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ23" s="15"/>
+      <c r="AR23" s="15"/>
+      <c r="AS23" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT23" s="15"/>
+      <c r="AU23" s="15"/>
+      <c r="AV23" s="15"/>
+      <c r="AW23" s="15"/>
+      <c r="AX23" s="15"/>
+      <c r="AY23" s="15"/>
+      <c r="AZ23" s="15"/>
+      <c r="BA23" s="15"/>
+      <c r="BB23" s="15"/>
+      <c r="BC23" s="15"/>
+      <c r="BD23" s="15"/>
+      <c r="BE23" s="15"/>
+      <c r="BF23" s="15"/>
+      <c r="BG23" s="15"/>
+      <c r="BH23" s="15"/>
+      <c r="BI23" s="15"/>
+      <c r="BJ23" s="15"/>
+      <c r="BK23" s="15"/>
+      <c r="BL23" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <autoFilter ref="A1:BL1"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8Tour Standard — 22 étages, 2 cages d'escalier, garage souterrain&amp;C&amp;8Matrice causes-effets — alarme incendie&amp;R&amp;82026-07-03</oddHeader>
+    <oddFooter>&amp;L&amp;8À valider par l'ingénieur au dossier&amp;C&amp;8&amp;P / &amp;N&amp;R&amp;8Confidentiel — usage interne du projet</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="G31" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C34" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="G35" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="F40" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C46" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="F53" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="G54" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="G55" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="G56" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="G57" s="26" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D58" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G59" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="G60" s="26" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="26" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="G62" s="26" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -4849,145 +7171,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>133</v>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="41" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -4996,9 +7338,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -5006,179 +7348,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>165</v>
+      <c r="A1" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="32" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>168</v>
+      <c r="A3" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>170</v>
+      <c r="A4" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>172</v>
+      <c r="A5" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>174</v>
+      <c r="A6" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>176</v>
+      <c r="A7" s="31" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>178</v>
+      <c r="A8" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>174</v>
+      <c r="A9" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>174</v>
+      <c r="A10" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>174</v>
+      <c r="A11" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>174</v>
+      <c r="A12" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>174</v>
+      <c r="A13" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>174</v>
+      <c r="A14" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>174</v>
+      <c r="A15" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>174</v>
+      <c r="A16" s="31" t="s">
+        <v>355</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>174</v>
+      <c r="A17" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>174</v>
+      <c r="A18" s="31" t="s">
+        <v>357</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>174</v>
+      <c r="A19" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>174</v>
+      <c r="A20" s="31" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>192</v>
+      <c r="A21" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>194</v>
+      <c r="A22" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -5187,7 +7553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -5198,393 +7564,393 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>197</v>
+      <c r="A1" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="B2" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>200</v>
+      <c r="A2" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>203</v>
+      <c r="A3" s="42" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>203</v>
+      <c r="A4" s="42" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>203</v>
+      <c r="A5" s="42" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>208</v>
+      <c r="A6" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>211</v>
+      <c r="A7" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>203</v>
+      <c r="A8" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>203</v>
+      <c r="A9" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>215</v>
+      <c r="A10" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>203</v>
+      <c r="A11" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>203</v>
+      <c r="A12" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>203</v>
+      <c r="A13" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>220</v>
+      <c r="A14" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>203</v>
+      <c r="A15" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>203</v>
+      <c r="A16" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>203</v>
+      <c r="A17" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>203</v>
+      <c r="A18" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>203</v>
+      <c r="A19" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>397</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>203</v>
+      <c r="A20" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>203</v>
+      <c r="A21" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>203</v>
+      <c r="A22" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>230</v>
+      <c r="A23" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>203</v>
+      <c r="A24" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>203</v>
+      <c r="A25" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>203</v>
+      <c r="A26" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>405</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>203</v>
+      <c r="A27" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>236</v>
+      <c r="A28" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>407</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>203</v>
+      <c r="A29" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>409</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>203</v>
+      <c r="A30" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>203</v>
+      <c r="A31" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>203</v>
+      <c r="A32" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>243</v>
+      <c r="A33" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>246</v>
+      <c r="A34" s="42" t="s">
+        <v>416</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>249</v>
+      <c r="A35" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>420</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>250</v>
+        <v>422</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
